--- a/bus-service-management-system/src/main/resources/excel/lineBusStopsReport.xlsx
+++ b/bus-service-management-system/src/main/resources/excel/lineBusStopsReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\bus-service-management-system\src\main\resources\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\busServiceManagement\src\main\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D810DA-A886-41A1-A58E-907641D0B306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB0E02C-A50F-406D-82C2-E44729FD6CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18228" windowHeight="13680" xr2:uid="{5ABEEBCB-3930-45F1-B634-347EAEF54C96}"/>
+    <workbookView xWindow="885" yWindow="915" windowWidth="21600" windowHeight="13500" xr2:uid="{5ABEEBCB-3930-45F1-B634-347EAEF54C96}"/>
   </bookViews>
   <sheets>
     <sheet name="停留所情報インポート" sheetId="1" r:id="rId1"/>
@@ -1323,18 +1323,18 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:Z5"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="14.3984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" style="3" customWidth="1"/>
-    <col min="4" max="7" width="14.3984375" style="3" customWidth="1"/>
+    <col min="1" max="2" width="14.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="3" customWidth="1"/>
+    <col min="4" max="7" width="14.375" style="3" customWidth="1"/>
     <col min="8" max="8" width="15.5" style="3" customWidth="1"/>
-    <col min="9" max="10" width="14.3984375" style="3" customWidth="1"/>
+    <col min="9" max="10" width="14.375" style="3" customWidth="1"/>
     <col min="11" max="20" width="14.5" style="3" customWidth="1"/>
     <col min="21" max="21" width="15" style="3" customWidth="1"/>
-    <col min="22" max="22" width="25.8984375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="25.875" style="3" customWidth="1"/>
     <col min="23" max="28" width="14.5" style="3" customWidth="1"/>
-    <col min="29" max="16384" width="8.59765625" style="3"/>
+    <col min="29" max="16384" width="8.625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -1362,7 +1362,7 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="4" t="s">
